--- a/Excel/StartSceneConfig@s.xlsx
+++ b/Excel/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9495" windowHeight="5595"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>LoginCenter</t>
+  </si>
+  <si>
+    <t>UnitChache</t>
   </si>
   <si>
     <t>Robot</t>
@@ -826,7 +829,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1105,7 +1108,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:H13"/>
+  <dimension ref="C3:H14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1327,6 +1330,24 @@
         <v>22</v>
       </c>
       <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="3:8">
+      <c r="C14" s="3">
+        <v>9</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1420,10 +1441,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartSceneConfig@s.xlsx
+++ b/Excel/StartSceneConfig@s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>UnitChache</t>
+  </si>
+  <si>
+    <t>Game</t>
   </si>
   <si>
     <t>Robot</t>
@@ -829,7 +832,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1108,7 +1111,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:H14"/>
+  <dimension ref="C3:H15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1348,6 +1351,24 @@
         <v>23</v>
       </c>
       <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="3:8">
+      <c r="C15" s="3">
+        <v>10</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1441,10 +1462,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartSceneConfig@s.xlsx
+++ b/Excel/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="22635" windowHeight="7710"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Game</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>Robot</t>
@@ -832,7 +835,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1111,7 +1114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:H15"/>
+  <dimension ref="C3:H35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1339,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5">
         <v>1</v>
@@ -1369,6 +1372,76 @@
         <v>24</v>
       </c>
       <c r="H15" s="5"/>
+    </row>
+    <row r="26" spans="4:8">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="4:8">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="4:8">
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="4:8">
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="4:8">
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="4:8">
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="4:8">
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="4:8">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="4:8">
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="4:8">
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1380,7 +1453,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:H6"/>
+  <dimension ref="B3:H6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1451,7 +1524,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:8">
+    <row r="6" s="1" customFormat="1" spans="2:8">
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="C6" s="5">
         <v>200</v>
       </c>
@@ -1462,10 +1538,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartSceneConfig@s.xlsx
+++ b/Excel/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22635" windowHeight="7710"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -835,7 +835,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1342,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5">
         <v>1</v>

--- a/Excel/StartSceneConfig@s.xlsx
+++ b/Excel/StartSceneConfig@s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Game</t>
+  </si>
+  <si>
+    <t>Rank</t>
   </si>
   <si>
     <t>#</t>
@@ -1373,6 +1376,24 @@
       </c>
       <c r="H15" s="5"/>
     </row>
+    <row r="16" spans="3:8">
+      <c r="C16" s="3">
+        <v>11</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="5"/>
+    </row>
     <row r="26" spans="4:8">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1526,7 +1547,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="2:8">
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5">
         <v>200</v>
@@ -1538,10 +1559,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartSceneConfig@s.xlsx
+++ b/Excel/StartSceneConfig@s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Rank</t>
+  </si>
+  <si>
+    <t>Chat</t>
   </si>
   <si>
     <t>#</t>
@@ -1394,6 +1397,23 @@
       </c>
       <c r="H16" s="5"/>
     </row>
+    <row r="17" spans="3:7">
+      <c r="C17" s="3">
+        <v>12</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="26" spans="4:8">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1547,7 +1567,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="2:8">
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="5">
         <v>200</v>
@@ -1559,10 +1579,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="5"/>
     </row>
